--- a/data/donnees_fusionnees.xlsx
+++ b/data/donnees_fusionnees.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt formatCode="yyyy-mm-dd h:mm:ss" numFmtId="164"/>
+    <numFmt formatCode="YYYY-MM-DD HH:MM:SS" numFmtId="165"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -53,18 +56,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L162"/>
+  <dimension ref="A1:N162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +493,16 @@
           <t>pratique_sport</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>distance_domicile_entreprise_km</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>erreur_declaration_transport</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -504,20 +518,16 @@
           <t>Audrey</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1990-07-06</t>
-        </is>
+      <c r="D2" s="2" t="n">
+        <v>33060</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2020-12-14</t>
-        </is>
+      <c r="F2" s="2" t="n">
+        <v>44179</v>
       </c>
       <c r="G2" t="n">
         <v>30940</v>
@@ -537,13 +547,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M2" t="n">
+        <v>26.703</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -560,20 +576,16 @@
           <t>Monique</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1962-01-06</t>
-        </is>
+      <c r="D3" s="2" t="n">
+        <v>22652</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2020-07-07</t>
-        </is>
+      <c r="F3" s="2" t="n">
+        <v>44019</v>
       </c>
       <c r="G3" t="n">
         <v>74360</v>
@@ -593,13 +605,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M3" t="n">
+        <v>22.645</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -616,20 +634,16 @@
           <t>Michelle</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1976-08-09</t>
-        </is>
+      <c r="D4" s="2" t="n">
+        <v>27981</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
+      <c r="F4" s="2" t="n">
+        <v>44649</v>
       </c>
       <c r="G4" t="n">
         <v>51390</v>
@@ -649,13 +663,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>TENNIS</t>
         </is>
+      </c>
+      <c r="M4" t="n">
+        <v>48.718</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -672,20 +692,16 @@
           <t>Judith</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1962-09-10</t>
-        </is>
+      <c r="D5" s="2" t="n">
+        <v>22899</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2021-12-12</t>
-        </is>
+      <c r="F5" s="2" t="n">
+        <v>44542</v>
       </c>
       <c r="G5" t="n">
         <v>70320</v>
@@ -705,13 +721,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M5" t="n">
+        <v>1.628</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -728,20 +750,16 @@
           <t>Michelle</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1975-04-20</t>
-        </is>
+      <c r="D6" s="2" t="n">
+        <v>27504</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2025-02-19</t>
-        </is>
+      <c r="F6" s="2" t="n">
+        <v>45707</v>
       </c>
       <c r="G6" t="n">
         <v>46870</v>
@@ -761,13 +779,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -784,20 +808,16 @@
           <t>Margaret</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1982-11-24</t>
-        </is>
+      <c r="D7" s="2" t="n">
+        <v>30279</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2023-04-17</t>
-        </is>
+      <c r="F7" s="2" t="n">
+        <v>45033</v>
       </c>
       <c r="G7" t="n">
         <v>31460</v>
@@ -817,13 +837,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>BADMINTON</t>
         </is>
+      </c>
+      <c r="M7" t="n">
+        <v>5.173</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -840,20 +866,16 @@
           <t>Julien</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1970-12-19</t>
-        </is>
+      <c r="D8" s="2" t="n">
+        <v>25921</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2021-08-21</t>
-        </is>
+      <c r="F8" s="2" t="n">
+        <v>44429</v>
       </c>
       <c r="G8" t="n">
         <v>72480</v>
@@ -873,13 +895,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>ESCALADE</t>
         </is>
+      </c>
+      <c r="M8" t="n">
+        <v>38.534</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -896,20 +924,16 @@
           <t>Brigitte</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1977-12-27</t>
-        </is>
+      <c r="D9" s="2" t="n">
+        <v>28486</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2020-05-26</t>
-        </is>
+      <c r="F9" s="2" t="n">
+        <v>43977</v>
       </c>
       <c r="G9" t="n">
         <v>59790</v>
@@ -929,13 +953,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M9" t="n">
+        <v>30.104</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -952,20 +982,16 @@
           <t>Jérome</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1979-02-01</t>
-        </is>
+      <c r="D10" s="2" t="n">
+        <v>28887</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2020-09-07</t>
-        </is>
+      <c r="F10" s="2" t="n">
+        <v>44081</v>
       </c>
       <c r="G10" t="n">
         <v>29240</v>
@@ -985,13 +1011,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M10" t="n">
+        <v>30.065</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1008,20 +1040,16 @@
           <t>Zakaria</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>1987-10-02</t>
-        </is>
+      <c r="D11" s="2" t="n">
+        <v>32052</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2024-11-23</t>
-        </is>
+      <c r="F11" s="2" t="n">
+        <v>45619</v>
       </c>
       <c r="G11" t="n">
         <v>68680</v>
@@ -1041,13 +1069,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M11" t="n">
+        <v>9.116</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1064,20 +1098,16 @@
           <t>Aurélie</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1999-01-26</t>
-        </is>
+      <c r="D12" s="2" t="n">
+        <v>36186</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2025-01-02</t>
-        </is>
+      <c r="F12" s="2" t="n">
+        <v>45659</v>
       </c>
       <c r="G12" t="n">
         <v>56400</v>
@@ -1097,13 +1127,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M12" t="n">
+        <v>8.231999999999999</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1120,20 +1156,16 @@
           <t>Augustin</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1987-03-05</t>
-        </is>
+      <c r="D13" s="2" t="n">
+        <v>31841</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2023-10-27</t>
-        </is>
+      <c r="F13" s="2" t="n">
+        <v>45226</v>
       </c>
       <c r="G13" t="n">
         <v>31030</v>
@@ -1153,13 +1185,19 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>TRIATHLON</t>
         </is>
+      </c>
+      <c r="M13" t="n">
+        <v>11.574</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1176,20 +1214,16 @@
           <t>Francoise</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1986-11-11</t>
-        </is>
+      <c r="D14" s="2" t="n">
+        <v>31727</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2025-01-11</t>
-        </is>
+      <c r="F14" s="2" t="n">
+        <v>45668</v>
       </c>
       <c r="G14" t="n">
         <v>30680</v>
@@ -1209,13 +1243,19 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1.537</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1232,20 +1272,16 @@
           <t>Yves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1998-11-18</t>
-        </is>
+      <c r="D15" s="2" t="n">
+        <v>36117</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2020-08-14</t>
-        </is>
+      <c r="F15" s="2" t="n">
+        <v>44057</v>
       </c>
       <c r="G15" t="n">
         <v>50170</v>
@@ -1265,13 +1301,19 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M15" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1288,20 +1330,16 @@
           <t>Benoit</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1981-03-31</t>
-        </is>
+      <c r="D16" s="2" t="n">
+        <v>29676</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2025-03-24</t>
-        </is>
+      <c r="F16" s="2" t="n">
+        <v>45740</v>
       </c>
       <c r="G16" t="n">
         <v>62670</v>
@@ -1321,13 +1359,19 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M16" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1344,20 +1388,16 @@
           <t>Antoine</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1982-03-11</t>
-        </is>
+      <c r="D17" s="2" t="n">
+        <v>30021</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2021-01-12</t>
-        </is>
+      <c r="F17" s="2" t="n">
+        <v>44208</v>
       </c>
       <c r="G17" t="n">
         <v>29440</v>
@@ -1377,13 +1417,19 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M17" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1400,20 +1446,16 @@
           <t>Eugénie</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1971-04-25</t>
-        </is>
+      <c r="D18" s="2" t="n">
+        <v>26048</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2021-06-22</t>
-        </is>
+      <c r="F18" s="2" t="n">
+        <v>44369</v>
       </c>
       <c r="G18" t="n">
         <v>56470</v>
@@ -1433,13 +1475,19 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M18" t="n">
+        <v>50.758</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1456,20 +1504,16 @@
           <t>Léon</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1962-03-01</t>
-        </is>
+      <c r="D19" s="2" t="n">
+        <v>22706</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2025-02-02</t>
-        </is>
+      <c r="F19" s="2" t="n">
+        <v>45690</v>
       </c>
       <c r="G19" t="n">
         <v>67110</v>
@@ -1489,13 +1533,19 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M19" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1512,20 +1562,16 @@
           <t>Francoise</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1970-07-01</t>
-        </is>
+      <c r="D20" s="2" t="n">
+        <v>25750</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2021-05-25</t>
-        </is>
+      <c r="F20" s="2" t="n">
+        <v>44341</v>
       </c>
       <c r="G20" t="n">
         <v>44040</v>
@@ -1545,13 +1591,19 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>ÉQUITATION</t>
         </is>
+      </c>
+      <c r="M20" t="n">
+        <v>20.772</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1568,20 +1620,16 @@
           <t>Claire</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1970-05-03</t>
-        </is>
+      <c r="D21" s="2" t="n">
+        <v>25691</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2021-03-10</t>
-        </is>
+      <c r="F21" s="2" t="n">
+        <v>44265</v>
       </c>
       <c r="G21" t="n">
         <v>62760</v>
@@ -1601,13 +1649,19 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>VOILE</t>
         </is>
+      </c>
+      <c r="M21" t="n">
+        <v>50.159</v>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1624,20 +1678,16 @@
           <t>Victor</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1972-04-26</t>
-        </is>
+      <c r="D22" s="2" t="n">
+        <v>26415</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2024-09-28</t>
-        </is>
+      <c r="F22" s="2" t="n">
+        <v>45563</v>
       </c>
       <c r="G22" t="n">
         <v>33620</v>
@@ -1657,13 +1707,19 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M22" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1680,20 +1736,16 @@
           <t>Alice</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1994-12-21</t>
-        </is>
+      <c r="D23" s="2" t="n">
+        <v>34689</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2020-12-06</t>
-        </is>
+      <c r="F23" s="2" t="n">
+        <v>44171</v>
       </c>
       <c r="G23" t="n">
         <v>73720</v>
@@ -1713,13 +1765,19 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M23" t="n">
+        <v>14.515</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1736,20 +1794,16 @@
           <t>Michelle</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1989-01-20</t>
-        </is>
+      <c r="D24" s="2" t="n">
+        <v>32528</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2024-12-29</t>
-        </is>
+      <c r="F24" s="2" t="n">
+        <v>45655</v>
       </c>
       <c r="G24" t="n">
         <v>73160</v>
@@ -1769,13 +1823,19 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M24" t="n">
+        <v>3.035</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1792,20 +1852,16 @@
           <t>Mathilde</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1974-10-15</t>
-        </is>
+      <c r="D25" s="2" t="n">
+        <v>27317</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2023-04-02</t>
-        </is>
+      <c r="F25" s="2" t="n">
+        <v>45018</v>
       </c>
       <c r="G25" t="n">
         <v>27040</v>
@@ -1825,13 +1881,19 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>TENNIS DE TABLE</t>
         </is>
+      </c>
+      <c r="M25" t="n">
+        <v>6.776</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1848,20 +1910,16 @@
           <t>Robert</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1984-08-23</t>
-        </is>
+      <c r="D26" s="2" t="n">
+        <v>30917</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2021-07-14</t>
-        </is>
+      <c r="F26" s="2" t="n">
+        <v>44391</v>
       </c>
       <c r="G26" t="n">
         <v>49610</v>
@@ -1881,13 +1939,19 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M26" t="n">
+        <v>6.668</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1904,20 +1968,16 @@
           <t>Claudine</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1981-08-15</t>
-        </is>
+      <c r="D27" s="2" t="n">
+        <v>29813</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2023-01-13</t>
-        </is>
+      <c r="F27" s="2" t="n">
+        <v>44939</v>
       </c>
       <c r="G27" t="n">
         <v>43710</v>
@@ -1937,13 +1997,19 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>FOOTBALL</t>
         </is>
+      </c>
+      <c r="M27" t="n">
+        <v>11.133</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1960,20 +2026,16 @@
           <t>Benjamin</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1996-12-10</t>
-        </is>
+      <c r="D28" s="2" t="n">
+        <v>35409</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2020-11-14</t>
-        </is>
+      <c r="F28" s="2" t="n">
+        <v>44149</v>
       </c>
       <c r="G28" t="n">
         <v>65310</v>
@@ -1993,13 +2055,19 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M28" t="n">
+        <v>4.435</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2016,20 +2084,16 @@
           <t>Léa</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1975-05-02</t>
-        </is>
+      <c r="D29" s="2" t="n">
+        <v>27516</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2020-10-05</t>
-        </is>
+      <c r="F29" s="2" t="n">
+        <v>44109</v>
       </c>
       <c r="G29" t="n">
         <v>43450</v>
@@ -2049,13 +2113,19 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M29" t="n">
+        <v>2.135</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2072,20 +2142,16 @@
           <t>Diane</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1971-09-18</t>
-        </is>
+      <c r="D30" s="2" t="n">
+        <v>26194</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2022-06-16</t>
-        </is>
+      <c r="F30" s="2" t="n">
+        <v>44728</v>
       </c>
       <c r="G30" t="n">
         <v>69760</v>
@@ -2105,13 +2171,19 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M30" t="n">
+        <v>58.621</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2128,20 +2200,16 @@
           <t>Gabriel</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1972-11-05</t>
-        </is>
+      <c r="D31" s="2" t="n">
+        <v>26608</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2023-12-29</t>
-        </is>
+      <c r="F31" s="2" t="n">
+        <v>45289</v>
       </c>
       <c r="G31" t="n">
         <v>67610</v>
@@ -2161,13 +2229,19 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>VOILE</t>
         </is>
+      </c>
+      <c r="M31" t="n">
+        <v>66.218</v>
+      </c>
+      <c r="N31" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2184,20 +2258,16 @@
           <t>Brigitte</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1978-05-24</t>
-        </is>
+      <c r="D32" s="2" t="n">
+        <v>28634</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2023-07-15</t>
-        </is>
+      <c r="F32" s="2" t="n">
+        <v>45122</v>
       </c>
       <c r="G32" t="n">
         <v>71040</v>
@@ -2217,13 +2287,19 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M32" t="n">
+        <v>4.451</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2240,20 +2316,16 @@
           <t>Maurice</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1973-12-18</t>
-        </is>
+      <c r="D33" s="2" t="n">
+        <v>27016</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2024-11-26</t>
-        </is>
+      <c r="F33" s="2" t="n">
+        <v>45622</v>
       </c>
       <c r="G33" t="n">
         <v>63860</v>
@@ -2273,13 +2345,19 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>FOOTBALL</t>
         </is>
+      </c>
+      <c r="M33" t="n">
+        <v>13.368</v>
+      </c>
+      <c r="N33" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2296,20 +2374,16 @@
           <t>Charles</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1978-12-22</t>
-        </is>
+      <c r="D34" s="2" t="n">
+        <v>28846</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2020-07-12</t>
-        </is>
+      <c r="F34" s="2" t="n">
+        <v>44024</v>
       </c>
       <c r="G34" t="n">
         <v>73490</v>
@@ -2329,13 +2403,19 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>TENNIS</t>
         </is>
+      </c>
+      <c r="M34" t="n">
+        <v>5.173</v>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2352,20 +2432,16 @@
           <t>Claire</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1997-05-05</t>
-        </is>
+      <c r="D35" s="2" t="n">
+        <v>35555</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2024-03-28</t>
-        </is>
+      <c r="F35" s="2" t="n">
+        <v>45379</v>
       </c>
       <c r="G35" t="n">
         <v>57460</v>
@@ -2385,13 +2461,19 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>TENNIS</t>
         </is>
+      </c>
+      <c r="M35" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="N35" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2408,20 +2490,16 @@
           <t>Alain</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1983-06-03</t>
-        </is>
+      <c r="D36" s="2" t="n">
+        <v>30470</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2021-11-04</t>
-        </is>
+      <c r="F36" s="2" t="n">
+        <v>44504</v>
       </c>
       <c r="G36" t="n">
         <v>43210</v>
@@ -2441,13 +2519,19 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M36" t="n">
+        <v>10.087</v>
+      </c>
+      <c r="N36" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2464,20 +2548,16 @@
           <t>Juliette</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1991-10-22</t>
-        </is>
+      <c r="D37" s="2" t="n">
+        <v>33533</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2025-03-06</t>
-        </is>
+      <c r="F37" s="2" t="n">
+        <v>45722</v>
       </c>
       <c r="G37" t="n">
         <v>57040</v>
@@ -2497,13 +2577,19 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M37" t="n">
+        <v>26.676</v>
+      </c>
+      <c r="N37" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2520,20 +2606,16 @@
           <t>Mégane</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1979-01-28</t>
-        </is>
+      <c r="D38" s="2" t="n">
+        <v>28883</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2023-01-25</t>
-        </is>
+      <c r="F38" s="2" t="n">
+        <v>44951</v>
       </c>
       <c r="G38" t="n">
         <v>33850</v>
@@ -2553,13 +2635,19 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M38" t="n">
+        <v>8.420999999999999</v>
+      </c>
+      <c r="N38" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2576,20 +2664,16 @@
           <t>Francoise</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1999-11-13</t>
-        </is>
+      <c r="D39" s="2" t="n">
+        <v>36477</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2023-01-26</t>
-        </is>
+      <c r="F39" s="2" t="n">
+        <v>44952</v>
       </c>
       <c r="G39" t="n">
         <v>30560</v>
@@ -2609,13 +2693,19 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M39" t="n">
+        <v>12.912</v>
+      </c>
+      <c r="N39" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2632,20 +2722,16 @@
           <t>Andréa</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1985-01-17</t>
-        </is>
+      <c r="D40" s="2" t="n">
+        <v>31064</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2023-02-12</t>
-        </is>
+      <c r="F40" s="2" t="n">
+        <v>44969</v>
       </c>
       <c r="G40" t="n">
         <v>55670</v>
@@ -2665,13 +2751,19 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M40" t="n">
+        <v>14.986</v>
+      </c>
+      <c r="N40" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2688,20 +2780,16 @@
           <t>Monique</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1986-04-27</t>
-        </is>
+      <c r="D41" s="2" t="n">
+        <v>31529</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2024-02-22</t>
-        </is>
+      <c r="F41" s="2" t="n">
+        <v>45344</v>
       </c>
       <c r="G41" t="n">
         <v>54710</v>
@@ -2721,13 +2809,19 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M41" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="N41" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2744,20 +2838,16 @@
           <t>Constance</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1976-02-16</t>
-        </is>
+      <c r="D42" s="2" t="n">
+        <v>27806</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2024-09-02</t>
-        </is>
+      <c r="F42" s="2" t="n">
+        <v>45537</v>
       </c>
       <c r="G42" t="n">
         <v>70060</v>
@@ -2777,13 +2867,19 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M42" t="n">
+        <v>16.896</v>
+      </c>
+      <c r="N42" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2800,20 +2896,16 @@
           <t>Marcel</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1971-05-20</t>
-        </is>
+      <c r="D43" s="2" t="n">
+        <v>26073</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2021-08-12</t>
-        </is>
+      <c r="F43" s="2" t="n">
+        <v>44420</v>
       </c>
       <c r="G43" t="n">
         <v>38870</v>
@@ -2833,13 +2925,19 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M43" t="n">
+        <v>74.48699999999999</v>
+      </c>
+      <c r="N43" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2856,20 +2954,16 @@
           <t>Marine</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1972-01-17</t>
-        </is>
+      <c r="D44" s="2" t="n">
+        <v>26315</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2021-09-10</t>
-        </is>
+      <c r="F44" s="2" t="n">
+        <v>44449</v>
       </c>
       <c r="G44" t="n">
         <v>50700</v>
@@ -2889,13 +2983,19 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>NATATION</t>
         </is>
+      </c>
+      <c r="M44" t="n">
+        <v>18.551</v>
+      </c>
+      <c r="N44" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2912,20 +3012,16 @@
           <t>Andre</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1977-09-15</t>
-        </is>
+      <c r="D45" s="2" t="n">
+        <v>28383</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2021-06-30</t>
-        </is>
+      <c r="F45" s="2" t="n">
+        <v>44377</v>
       </c>
       <c r="G45" t="n">
         <v>58580</v>
@@ -2945,13 +3041,19 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>BADMINTON</t>
         </is>
+      </c>
+      <c r="M45" t="n">
+        <v>12.906</v>
+      </c>
+      <c r="N45" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2968,20 +3070,16 @@
           <t>Louis</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1984-07-03</t>
-        </is>
+      <c r="D46" s="2" t="n">
+        <v>30866</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2022-09-03</t>
-        </is>
+      <c r="F46" s="2" t="n">
+        <v>44807</v>
       </c>
       <c r="G46" t="n">
         <v>33450</v>
@@ -3001,13 +3099,19 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M46" t="n">
+        <v>8.986000000000001</v>
+      </c>
+      <c r="N46" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3024,20 +3128,16 @@
           <t>William</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>1973-03-10</t>
-        </is>
+      <c r="D47" s="2" t="n">
+        <v>26733</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2025-03-24</t>
-        </is>
+      <c r="F47" s="2" t="n">
+        <v>45740</v>
       </c>
       <c r="G47" t="n">
         <v>68120</v>
@@ -3057,13 +3157,19 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M47" t="n">
+        <v>2.366</v>
+      </c>
+      <c r="N47" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3080,20 +3186,16 @@
           <t>Jules</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>1999-03-11</t>
-        </is>
+      <c r="D48" s="2" t="n">
+        <v>36230</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2024-11-19</t>
-        </is>
+      <c r="F48" s="2" t="n">
+        <v>45615</v>
       </c>
       <c r="G48" t="n">
         <v>42410</v>
@@ -3113,13 +3215,19 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>NATATION</t>
         </is>
+      </c>
+      <c r="M48" t="n">
+        <v>1.628</v>
+      </c>
+      <c r="N48" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3136,20 +3244,16 @@
           <t>Denise</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>1987-09-05</t>
-        </is>
+      <c r="D49" s="2" t="n">
+        <v>32025</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2021-07-01</t>
-        </is>
+      <c r="F49" s="2" t="n">
+        <v>44378</v>
       </c>
       <c r="G49" t="n">
         <v>38930</v>
@@ -3169,13 +3273,19 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>TENNIS DE TABLE</t>
         </is>
+      </c>
+      <c r="M49" t="n">
+        <v>10.76</v>
+      </c>
+      <c r="N49" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3192,20 +3302,16 @@
           <t>Olivie</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>1964-09-22</t>
-        </is>
+      <c r="D50" s="2" t="n">
+        <v>23642</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2021-07-05</t>
-        </is>
+      <c r="F50" s="2" t="n">
+        <v>44382</v>
       </c>
       <c r="G50" t="n">
         <v>32520</v>
@@ -3225,13 +3331,19 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M50" t="n">
+        <v>76.67400000000001</v>
+      </c>
+      <c r="N50" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3248,20 +3360,16 @@
           <t>Paul</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1980-05-18</t>
-        </is>
+      <c r="D51" s="2" t="n">
+        <v>29359</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2020-11-12</t>
-        </is>
+      <c r="F51" s="2" t="n">
+        <v>44147</v>
       </c>
       <c r="G51" t="n">
         <v>36430</v>
@@ -3281,13 +3389,19 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>BADMINTON</t>
         </is>
+      </c>
+      <c r="M51" t="n">
+        <v>6.428</v>
+      </c>
+      <c r="N51" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3304,20 +3418,16 @@
           <t>Christine</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2001-03-08</t>
-        </is>
+      <c r="D52" s="2" t="n">
+        <v>36958</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2024-12-10</t>
-        </is>
+      <c r="F52" s="2" t="n">
+        <v>45636</v>
       </c>
       <c r="G52" t="n">
         <v>43810</v>
@@ -3337,13 +3447,19 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M52" t="n">
+        <v>66.188</v>
+      </c>
+      <c r="N52" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3360,20 +3476,16 @@
           <t>Julie</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>1995-04-19</t>
-        </is>
+      <c r="D53" s="2" t="n">
+        <v>34808</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2022-09-04</t>
-        </is>
+      <c r="F53" s="2" t="n">
+        <v>44808</v>
       </c>
       <c r="G53" t="n">
         <v>36180</v>
@@ -3393,13 +3505,19 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>TENNIS</t>
         </is>
+      </c>
+      <c r="M53" t="n">
+        <v>8.885</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3416,20 +3534,16 @@
           <t>Yves</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>1969-02-28</t>
-        </is>
+      <c r="D54" s="2" t="n">
+        <v>25262</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2022-11-28</t>
-        </is>
+      <c r="F54" s="2" t="n">
+        <v>44893</v>
       </c>
       <c r="G54" t="n">
         <v>66130</v>
@@ -3449,13 +3563,19 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M54" t="n">
+        <v>18.507</v>
+      </c>
+      <c r="N54" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3472,20 +3592,16 @@
           <t>Jeremy</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>1989-05-13</t>
-        </is>
+      <c r="D55" s="2" t="n">
+        <v>32641</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2020-03-31</t>
-        </is>
+      <c r="F55" s="2" t="n">
+        <v>43921</v>
       </c>
       <c r="G55" t="n">
         <v>29180</v>
@@ -3505,13 +3621,19 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>FOOTBALL</t>
         </is>
+      </c>
+      <c r="M55" t="n">
+        <v>41.742</v>
+      </c>
+      <c r="N55" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3528,20 +3650,16 @@
           <t>Elodie</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1970-06-17</t>
-        </is>
+      <c r="D56" s="2" t="n">
+        <v>25736</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2024-11-16</t>
-        </is>
+      <c r="F56" s="2" t="n">
+        <v>45612</v>
       </c>
       <c r="G56" t="n">
         <v>42910</v>
@@ -3561,13 +3679,19 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M56" t="n">
+        <v>10.553</v>
+      </c>
+      <c r="N56" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3584,20 +3708,16 @@
           <t>Julien</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1986-08-21</t>
-        </is>
+      <c r="D57" s="2" t="n">
+        <v>31645</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2024-09-26</t>
-        </is>
+      <c r="F57" s="2" t="n">
+        <v>45561</v>
       </c>
       <c r="G57" t="n">
         <v>31700</v>
@@ -3617,13 +3737,19 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>VOILE</t>
         </is>
+      </c>
+      <c r="M57" t="n">
+        <v>11.749</v>
+      </c>
+      <c r="N57" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3640,20 +3766,16 @@
           <t>Henriette</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>1972-03-27</t>
-        </is>
+      <c r="D58" s="2" t="n">
+        <v>26385</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2021-07-31</t>
-        </is>
+      <c r="F58" s="2" t="n">
+        <v>44408</v>
       </c>
       <c r="G58" t="n">
         <v>74990</v>
@@ -3673,13 +3795,19 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M58" t="n">
+        <v>33.708</v>
+      </c>
+      <c r="N58" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3696,20 +3824,16 @@
           <t>Naomie</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1963-09-13</t>
-        </is>
+      <c r="D59" s="2" t="n">
+        <v>23267</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2020-08-10</t>
-        </is>
+      <c r="F59" s="2" t="n">
+        <v>44053</v>
       </c>
       <c r="G59" t="n">
         <v>25610</v>
@@ -3729,13 +3853,19 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>TENNIS</t>
         </is>
+      </c>
+      <c r="M59" t="n">
+        <v>33.942</v>
+      </c>
+      <c r="N59" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3752,20 +3882,16 @@
           <t>Adèle</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2000-05-28</t>
-        </is>
+      <c r="D60" s="2" t="n">
+        <v>36674</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2020-07-31</t>
-        </is>
+      <c r="F60" s="2" t="n">
+        <v>44043</v>
       </c>
       <c r="G60" t="n">
         <v>74300</v>
@@ -3785,13 +3911,19 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M60" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="N60" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3808,20 +3940,16 @@
           <t>Léon</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>1963-03-07</t>
-        </is>
+      <c r="D61" s="2" t="n">
+        <v>23077</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2022-06-29</t>
-        </is>
+      <c r="F61" s="2" t="n">
+        <v>44741</v>
       </c>
       <c r="G61" t="n">
         <v>27260</v>
@@ -3841,13 +3969,19 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M61" t="n">
+        <v>18.291</v>
+      </c>
+      <c r="N61" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3864,20 +3998,16 @@
           <t>Joseph</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>1995-12-19</t>
-        </is>
+      <c r="D62" s="2" t="n">
+        <v>35052</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2022-09-26</t>
-        </is>
+      <c r="F62" s="2" t="n">
+        <v>44830</v>
       </c>
       <c r="G62" t="n">
         <v>34610</v>
@@ -3897,13 +4027,19 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M62" t="n">
+        <v>7.926</v>
+      </c>
+      <c r="N62" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3920,20 +4056,16 @@
           <t>Arthur</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2002-08-04</t>
-        </is>
+      <c r="D63" s="2" t="n">
+        <v>37472</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2021-04-30</t>
-        </is>
+      <c r="F63" s="2" t="n">
+        <v>44316</v>
       </c>
       <c r="G63" t="n">
         <v>47370</v>
@@ -3953,13 +4085,19 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>JUDO</t>
         </is>
+      </c>
+      <c r="M63" t="n">
+        <v>53.057</v>
+      </c>
+      <c r="N63" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3976,20 +4114,16 @@
           <t>Nath</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>1961-03-27</t>
-        </is>
+      <c r="D64" s="2" t="n">
+        <v>22367</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2024-10-25</t>
-        </is>
+      <c r="F64" s="2" t="n">
+        <v>45590</v>
       </c>
       <c r="G64" t="n">
         <v>38670</v>
@@ -4009,13 +4143,19 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M64" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="N64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4032,20 +4172,16 @@
           <t>Roger</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>1967-09-15</t>
-        </is>
+      <c r="D65" s="2" t="n">
+        <v>24730</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2024-11-03</t>
-        </is>
+      <c r="F65" s="2" t="n">
+        <v>45599</v>
       </c>
       <c r="G65" t="n">
         <v>52770</v>
@@ -4065,13 +4201,19 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M65" t="n">
+        <v>22.283</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4088,20 +4230,16 @@
           <t>Hugues</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>1977-07-22</t>
-        </is>
+      <c r="D66" s="2" t="n">
+        <v>28328</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2023-02-08</t>
-        </is>
+      <c r="F66" s="2" t="n">
+        <v>44965</v>
       </c>
       <c r="G66" t="n">
         <v>62370</v>
@@ -4121,13 +4259,19 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M66" t="n">
+        <v>6.473</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4144,20 +4288,16 @@
           <t>Alphonse</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>1970-12-10</t>
-        </is>
+      <c r="D67" s="2" t="n">
+        <v>25912</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2020-05-26</t>
-        </is>
+      <c r="F67" s="2" t="n">
+        <v>43977</v>
       </c>
       <c r="G67" t="n">
         <v>30360</v>
@@ -4177,13 +4317,19 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M67" t="n">
+        <v>44.437</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4200,20 +4346,16 @@
           <t>Victor</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>1979-12-30</t>
-        </is>
+      <c r="D68" s="2" t="n">
+        <v>29219</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2020-11-08</t>
-        </is>
+      <c r="F68" s="2" t="n">
+        <v>44143</v>
       </c>
       <c r="G68" t="n">
         <v>60670</v>
@@ -4233,13 +4375,19 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>BASKETBALL</t>
         </is>
+      </c>
+      <c r="M68" t="n">
+        <v>49.056</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4256,20 +4404,16 @@
           <t>Julien</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>1969-03-25</t>
-        </is>
+      <c r="D69" s="2" t="n">
+        <v>25287</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2022-12-28</t>
-        </is>
+      <c r="F69" s="2" t="n">
+        <v>44923</v>
       </c>
       <c r="G69" t="n">
         <v>51610</v>
@@ -4289,13 +4433,19 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M69" t="n">
+        <v>65.51000000000001</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4312,20 +4462,16 @@
           <t>Antoine</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>1990-09-18</t>
-        </is>
+      <c r="D70" s="2" t="n">
+        <v>33134</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2021-02-15</t>
-        </is>
+      <c r="F70" s="2" t="n">
+        <v>44242</v>
       </c>
       <c r="G70" t="n">
         <v>37620</v>
@@ -4345,13 +4491,19 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M70" t="n">
+        <v>8.577</v>
+      </c>
+      <c r="N70" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4368,20 +4520,16 @@
           <t>Alexandre</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>1981-01-03</t>
-        </is>
+      <c r="D71" s="2" t="n">
+        <v>29589</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2021-07-08</t>
-        </is>
+      <c r="F71" s="2" t="n">
+        <v>44385</v>
       </c>
       <c r="G71" t="n">
         <v>28050</v>
@@ -4401,13 +4549,19 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M71" t="n">
+        <v>4.032</v>
+      </c>
+      <c r="N71" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4424,20 +4578,16 @@
           <t>Astrid</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>1972-01-31</t>
-        </is>
+      <c r="D72" s="2" t="n">
+        <v>26329</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2023-11-01</t>
-        </is>
+      <c r="F72" s="2" t="n">
+        <v>45231</v>
       </c>
       <c r="G72" t="n">
         <v>59520</v>
@@ -4457,13 +4607,19 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M72" t="n">
+        <v>12.426</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4480,20 +4636,16 @@
           <t>Christiane</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1994-04-18</t>
-        </is>
+      <c r="D73" s="2" t="n">
+        <v>34442</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2022-11-18</t>
-        </is>
+      <c r="F73" s="2" t="n">
+        <v>44883</v>
       </c>
       <c r="G73" t="n">
         <v>70550</v>
@@ -4513,13 +4665,19 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M73" t="n">
+        <v>16.759</v>
+      </c>
+      <c r="N73" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4536,20 +4694,16 @@
           <t>Charlene</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>1991-03-22</t>
-        </is>
+      <c r="D74" s="2" t="n">
+        <v>33319</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2022-04-22</t>
-        </is>
+      <c r="F74" s="2" t="n">
+        <v>44673</v>
       </c>
       <c r="G74" t="n">
         <v>43520</v>
@@ -4569,13 +4723,19 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M74" t="n">
+        <v>39.943</v>
+      </c>
+      <c r="N74" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4592,20 +4752,16 @@
           <t>Guillaume</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2002-01-21</t>
-        </is>
+      <c r="D75" s="2" t="n">
+        <v>37277</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2021-11-26</t>
-        </is>
+      <c r="F75" s="2" t="n">
+        <v>44526</v>
       </c>
       <c r="G75" t="n">
         <v>43860</v>
@@ -4625,13 +4781,19 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>JUDO</t>
         </is>
+      </c>
+      <c r="M75" t="n">
+        <v>39.842</v>
+      </c>
+      <c r="N75" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4648,20 +4810,16 @@
           <t>Alain</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>1983-02-22</t>
-        </is>
+      <c r="D76" s="2" t="n">
+        <v>30369</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2022-03-30</t>
-        </is>
+      <c r="F76" s="2" t="n">
+        <v>44650</v>
       </c>
       <c r="G76" t="n">
         <v>32350</v>
@@ -4681,13 +4839,19 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M76" t="n">
+        <v>5.018</v>
+      </c>
+      <c r="N76" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4704,20 +4868,16 @@
           <t>Thibaut</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>1992-01-19</t>
-        </is>
+      <c r="D77" s="2" t="n">
+        <v>33622</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2021-07-12</t>
-        </is>
+      <c r="F77" s="2" t="n">
+        <v>44389</v>
       </c>
       <c r="G77" t="n">
         <v>25730</v>
@@ -4737,13 +4897,19 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M77" t="n">
+        <v>6.744</v>
+      </c>
+      <c r="N77" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4760,20 +4926,16 @@
           <t>Mathilde</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>1981-09-04</t>
-        </is>
+      <c r="D78" s="2" t="n">
+        <v>29833</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
+      <c r="F78" s="2" t="n">
+        <v>44649</v>
       </c>
       <c r="G78" t="n">
         <v>44830</v>
@@ -4793,13 +4955,19 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>NATATION</t>
         </is>
+      </c>
+      <c r="M78" t="n">
+        <v>6.682</v>
+      </c>
+      <c r="N78" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4816,20 +4984,16 @@
           <t>Christiane</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1995-10-04</t>
-        </is>
+      <c r="D79" s="2" t="n">
+        <v>34976</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2021-09-04</t>
-        </is>
+      <c r="F79" s="2" t="n">
+        <v>44443</v>
       </c>
       <c r="G79" t="n">
         <v>37910</v>
@@ -4849,13 +5013,19 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>ESCALADE</t>
         </is>
+      </c>
+      <c r="M79" t="n">
+        <v>11.921</v>
+      </c>
+      <c r="N79" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4872,20 +5042,16 @@
           <t>Francis</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1977-01-30</t>
-        </is>
+      <c r="D80" s="2" t="n">
+        <v>28155</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2022-02-07</t>
-        </is>
+      <c r="F80" s="2" t="n">
+        <v>44599</v>
       </c>
       <c r="G80" t="n">
         <v>51800</v>
@@ -4905,13 +5071,19 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M80" t="n">
+        <v>34.398</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -4928,20 +5100,16 @@
           <t>Bernard</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>1976-09-11</t>
-        </is>
+      <c r="D81" s="2" t="n">
+        <v>28014</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2020-07-25</t>
-        </is>
+      <c r="F81" s="2" t="n">
+        <v>44037</v>
       </c>
       <c r="G81" t="n">
         <v>34230</v>
@@ -4961,13 +5129,19 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M81" t="n">
+        <v>7.489</v>
+      </c>
+      <c r="N81" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -4984,20 +5158,16 @@
           <t>Philippine</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1984-10-28</t>
-        </is>
+      <c r="D82" s="2" t="n">
+        <v>30983</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2023-10-16</t>
-        </is>
+      <c r="F82" s="2" t="n">
+        <v>45215</v>
       </c>
       <c r="G82" t="n">
         <v>73110</v>
@@ -5017,13 +5187,19 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>TENNIS</t>
         </is>
+      </c>
+      <c r="M82" t="n">
+        <v>18.498</v>
+      </c>
+      <c r="N82" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5040,20 +5216,16 @@
           <t>Hugues</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>1971-04-03</t>
-        </is>
+      <c r="D83" s="2" t="n">
+        <v>26026</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2022-04-04</t>
-        </is>
+      <c r="F83" s="2" t="n">
+        <v>44655</v>
       </c>
       <c r="G83" t="n">
         <v>72360</v>
@@ -5073,13 +5245,19 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>FOOTBALL</t>
         </is>
+      </c>
+      <c r="M83" t="n">
+        <v>4.858</v>
+      </c>
+      <c r="N83" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5096,20 +5274,16 @@
           <t>Audrey</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>1963-07-16</t>
-        </is>
+      <c r="D84" s="2" t="n">
+        <v>23208</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
+      <c r="F84" s="2" t="n">
+        <v>44826</v>
       </c>
       <c r="G84" t="n">
         <v>39290</v>
@@ -5129,13 +5303,19 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>TENNIS</t>
         </is>
+      </c>
+      <c r="M84" t="n">
+        <v>10.863</v>
+      </c>
+      <c r="N84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5152,20 +5332,16 @@
           <t>Thomas</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1979-11-17</t>
-        </is>
+      <c r="D85" s="2" t="n">
+        <v>29176</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2021-11-30</t>
-        </is>
+      <c r="F85" s="2" t="n">
+        <v>44530</v>
       </c>
       <c r="G85" t="n">
         <v>43530</v>
@@ -5185,13 +5361,19 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M85" t="n">
+        <v>25.107</v>
+      </c>
+      <c r="N85" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -5208,20 +5390,16 @@
           <t>Benjamin</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>1985-01-14</t>
-        </is>
+      <c r="D86" s="2" t="n">
+        <v>31061</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2021-07-03</t>
-        </is>
+      <c r="F86" s="2" t="n">
+        <v>44380</v>
       </c>
       <c r="G86" t="n">
         <v>25570</v>
@@ -5241,13 +5419,19 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M86" t="n">
+        <v>16.589</v>
+      </c>
+      <c r="N86" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5264,20 +5448,16 @@
           <t>Martin</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>1960-04-24</t>
-        </is>
+      <c r="D87" s="2" t="n">
+        <v>22030</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2022-11-05</t>
-        </is>
+      <c r="F87" s="2" t="n">
+        <v>44870</v>
       </c>
       <c r="G87" t="n">
         <v>47730</v>
@@ -5297,13 +5477,19 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M87" t="n">
+        <v>18.507</v>
+      </c>
+      <c r="N87" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -5320,20 +5506,16 @@
           <t>Capucine</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>1991-06-18</t>
-        </is>
+      <c r="D88" s="2" t="n">
+        <v>33407</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2022-12-04</t>
-        </is>
+      <c r="F88" s="2" t="n">
+        <v>44899</v>
       </c>
       <c r="G88" t="n">
         <v>48430</v>
@@ -5353,13 +5535,19 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>ÉQUITATION</t>
         </is>
+      </c>
+      <c r="M88" t="n">
+        <v>6.744</v>
+      </c>
+      <c r="N88" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5376,20 +5564,16 @@
           <t>Iris</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>1999-10-15</t>
-        </is>
+      <c r="D89" s="2" t="n">
+        <v>36448</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2024-03-18</t>
-        </is>
+      <c r="F89" s="2" t="n">
+        <v>45369</v>
       </c>
       <c r="G89" t="n">
         <v>74000</v>
@@ -5409,13 +5593,19 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M89" t="n">
+        <v>25.051</v>
+      </c>
+      <c r="N89" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5432,20 +5622,16 @@
           <t>Catherine</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>1970-01-18</t>
-        </is>
+      <c r="D90" s="2" t="n">
+        <v>25586</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2023-03-03</t>
-        </is>
+      <c r="F90" s="2" t="n">
+        <v>44988</v>
       </c>
       <c r="G90" t="n">
         <v>59240</v>
@@ -5465,13 +5651,19 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M90" t="n">
+        <v>50.758</v>
+      </c>
+      <c r="N90" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5488,20 +5680,16 @@
           <t>Henri</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>1962-10-07</t>
-        </is>
+      <c r="D91" s="2" t="n">
+        <v>22926</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2023-10-18</t>
-        </is>
+      <c r="F91" s="2" t="n">
+        <v>45217</v>
       </c>
       <c r="G91" t="n">
         <v>51630</v>
@@ -5521,13 +5709,19 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M91" t="n">
+        <v>65.358</v>
+      </c>
+      <c r="N91" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5544,20 +5738,16 @@
           <t>Claudine</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>1968-04-27</t>
-        </is>
+      <c r="D92" s="2" t="n">
+        <v>24955</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2020-09-20</t>
-        </is>
+      <c r="F92" s="2" t="n">
+        <v>44094</v>
       </c>
       <c r="G92" t="n">
         <v>68240</v>
@@ -5577,13 +5767,19 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>RUGBY</t>
         </is>
+      </c>
+      <c r="M92" t="n">
+        <v>5.158</v>
+      </c>
+      <c r="N92" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -5600,20 +5796,16 @@
           <t>André</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>1981-02-16</t>
-        </is>
+      <c r="D93" s="2" t="n">
+        <v>29633</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2020-08-29</t>
-        </is>
+      <c r="F93" s="2" t="n">
+        <v>44072</v>
       </c>
       <c r="G93" t="n">
         <v>74330</v>
@@ -5633,13 +5825,19 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>FOOTBALL</t>
         </is>
+      </c>
+      <c r="M93" t="n">
+        <v>8.587</v>
+      </c>
+      <c r="N93" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5656,20 +5854,16 @@
           <t>Danielle</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>1968-10-24</t>
-        </is>
+      <c r="D94" s="2" t="n">
+        <v>25135</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2023-09-23</t>
-        </is>
+      <c r="F94" s="2" t="n">
+        <v>45192</v>
       </c>
       <c r="G94" t="n">
         <v>29090</v>
@@ -5689,13 +5883,19 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M94" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="N94" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -5712,20 +5912,16 @@
           <t>Laure</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>1979-10-03</t>
-        </is>
+      <c r="D95" s="2" t="n">
+        <v>29131</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2022-08-07</t>
-        </is>
+      <c r="F95" s="2" t="n">
+        <v>44780</v>
       </c>
       <c r="G95" t="n">
         <v>51020</v>
@@ -5745,13 +5941,19 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M95" t="n">
+        <v>61.698</v>
+      </c>
+      <c r="N95" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5768,20 +5970,16 @@
           <t>Jules</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>1986-07-25</t>
-        </is>
+      <c r="D96" s="2" t="n">
+        <v>31618</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
+      <c r="F96" s="2" t="n">
+        <v>45387</v>
       </c>
       <c r="G96" t="n">
         <v>51010</v>
@@ -5801,13 +5999,19 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>VOILE</t>
         </is>
+      </c>
+      <c r="M96" t="n">
+        <v>12.448</v>
+      </c>
+      <c r="N96" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5824,20 +6028,16 @@
           <t>Susanne</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>1961-01-08</t>
-        </is>
+      <c r="D97" s="2" t="n">
+        <v>22289</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2025-01-15</t>
-        </is>
+      <c r="F97" s="2" t="n">
+        <v>45672</v>
       </c>
       <c r="G97" t="n">
         <v>55310</v>
@@ -5857,13 +6057,19 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>BADMINTON</t>
         </is>
+      </c>
+      <c r="M97" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N97" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5880,20 +6086,16 @@
           <t>Caroline</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>1987-05-30</t>
-        </is>
+      <c r="D98" s="2" t="n">
+        <v>31927</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2021-07-07</t>
-        </is>
+      <c r="F98" s="2" t="n">
+        <v>44384</v>
       </c>
       <c r="G98" t="n">
         <v>56010</v>
@@ -5913,13 +6115,19 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M98" t="n">
+        <v>70.012</v>
+      </c>
+      <c r="N98" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5936,20 +6144,16 @@
           <t>Colette</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>1971-08-28</t>
-        </is>
+      <c r="D99" s="2" t="n">
+        <v>26173</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2022-10-01</t>
-        </is>
+      <c r="F99" s="2" t="n">
+        <v>44835</v>
       </c>
       <c r="G99" t="n">
         <v>42280</v>
@@ -5969,13 +6173,19 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>BOXE</t>
         </is>
+      </c>
+      <c r="M99" t="n">
+        <v>45.201</v>
+      </c>
+      <c r="N99" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5992,20 +6202,16 @@
           <t>Margaud</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>1983-10-13</t>
-        </is>
+      <c r="D100" s="2" t="n">
+        <v>30602</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2020-05-19</t>
-        </is>
+      <c r="F100" s="2" t="n">
+        <v>43970</v>
       </c>
       <c r="G100" t="n">
         <v>47530</v>
@@ -6025,13 +6231,19 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>RUGBY</t>
         </is>
+      </c>
+      <c r="M100" t="n">
+        <v>4.407</v>
+      </c>
+      <c r="N100" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -6048,20 +6260,16 @@
           <t>Juliette</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>1993-11-06</t>
-        </is>
+      <c r="D101" s="2" t="n">
+        <v>34279</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2024-01-24</t>
-        </is>
+      <c r="F101" s="2" t="n">
+        <v>45315</v>
       </c>
       <c r="G101" t="n">
         <v>64970</v>
@@ -6081,13 +6289,19 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M101" t="n">
+        <v>10.303</v>
+      </c>
+      <c r="N101" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -6104,20 +6318,16 @@
           <t>Denise</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>1972-02-24</t>
-        </is>
+      <c r="D102" s="2" t="n">
+        <v>26353</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2020-09-01</t>
-        </is>
+      <c r="F102" s="2" t="n">
+        <v>44075</v>
       </c>
       <c r="G102" t="n">
         <v>42530</v>
@@ -6137,13 +6347,19 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>NATATION</t>
         </is>
+      </c>
+      <c r="M102" t="n">
+        <v>5.221</v>
+      </c>
+      <c r="N102" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -6160,20 +6376,16 @@
           <t>Hugues</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>1975-01-02</t>
-        </is>
+      <c r="D103" s="2" t="n">
+        <v>27396</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
+      <c r="F103" s="2" t="n">
+        <v>45572</v>
       </c>
       <c r="G103" t="n">
         <v>71640</v>
@@ -6193,13 +6405,19 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M103" t="n">
+        <v>11.616</v>
+      </c>
+      <c r="N103" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -6216,20 +6434,16 @@
           <t>Marine</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>1970-07-26</t>
-        </is>
+      <c r="D104" s="2" t="n">
+        <v>25775</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2023-09-14</t>
-        </is>
+      <c r="F104" s="2" t="n">
+        <v>45183</v>
       </c>
       <c r="G104" t="n">
         <v>47780</v>
@@ -6249,13 +6463,19 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M104" t="n">
+        <v>4.999</v>
+      </c>
+      <c r="N104" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -6272,20 +6492,16 @@
           <t>Sabine</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>1996-10-22</t>
-        </is>
+      <c r="D105" s="2" t="n">
+        <v>35360</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2023-12-29</t>
-        </is>
+      <c r="F105" s="2" t="n">
+        <v>45289</v>
       </c>
       <c r="G105" t="n">
         <v>55910</v>
@@ -6305,13 +6521,19 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M105" t="n">
+        <v>2.967</v>
+      </c>
+      <c r="N105" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -6328,20 +6550,16 @@
           <t>Nicole</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>1971-10-17</t>
-        </is>
+      <c r="D106" s="2" t="n">
+        <v>26223</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2021-08-09</t>
-        </is>
+      <c r="F106" s="2" t="n">
+        <v>44417</v>
       </c>
       <c r="G106" t="n">
         <v>45910</v>
@@ -6361,13 +6579,19 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M106" t="n">
+        <v>10.774</v>
+      </c>
+      <c r="N106" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -6384,20 +6608,16 @@
           <t>Charles</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>1997-02-09</t>
-        </is>
+      <c r="D107" s="2" t="n">
+        <v>35470</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2024-02-28</t>
-        </is>
+      <c r="F107" s="2" t="n">
+        <v>45350</v>
       </c>
       <c r="G107" t="n">
         <v>26830</v>
@@ -6417,13 +6637,19 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M107" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="N107" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -6440,20 +6666,16 @@
           <t>Valérie</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>1978-12-13</t>
-        </is>
+      <c r="D108" s="2" t="n">
+        <v>28837</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2021-06-05</t>
-        </is>
+      <c r="F108" s="2" t="n">
+        <v>44352</v>
       </c>
       <c r="G108" t="n">
         <v>38840</v>
@@ -6473,13 +6695,19 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M108" t="n">
+        <v>3.706</v>
+      </c>
+      <c r="N108" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -6496,20 +6724,16 @@
           <t>Sébastien</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>1984-12-27</t>
-        </is>
+      <c r="D109" s="2" t="n">
+        <v>31043</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2024-12-17</t>
-        </is>
+      <c r="F109" s="2" t="n">
+        <v>45643</v>
       </c>
       <c r="G109" t="n">
         <v>49630</v>
@@ -6529,13 +6753,19 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>TENNIS</t>
         </is>
+      </c>
+      <c r="M109" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="N109" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -6552,20 +6782,16 @@
           <t>Luc</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>1994-02-02</t>
-        </is>
+      <c r="D110" s="2" t="n">
+        <v>34367</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2022-04-06</t>
-        </is>
+      <c r="F110" s="2" t="n">
+        <v>44657</v>
       </c>
       <c r="G110" t="n">
         <v>71330</v>
@@ -6585,13 +6811,19 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>ESCALADE</t>
         </is>
+      </c>
+      <c r="M110" t="n">
+        <v>18.433</v>
+      </c>
+      <c r="N110" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -6608,20 +6840,16 @@
           <t>Dominique</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>1992-02-11</t>
-        </is>
+      <c r="D111" s="2" t="n">
+        <v>33645</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2024-10-22</t>
-        </is>
+      <c r="F111" s="2" t="n">
+        <v>45587</v>
       </c>
       <c r="G111" t="n">
         <v>51150</v>
@@ -6641,13 +6869,19 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M111" t="n">
+        <v>10.624</v>
+      </c>
+      <c r="N111" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -6664,20 +6898,16 @@
           <t>Margot</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>1980-06-28</t>
-        </is>
+      <c r="D112" s="2" t="n">
+        <v>29400</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2021-07-18</t>
-        </is>
+      <c r="F112" s="2" t="n">
+        <v>44395</v>
       </c>
       <c r="G112" t="n">
         <v>48700</v>
@@ -6697,13 +6927,19 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>BOXE</t>
         </is>
+      </c>
+      <c r="M112" t="n">
+        <v>24.084</v>
+      </c>
+      <c r="N112" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -6720,20 +6956,16 @@
           <t>Gilles</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>1961-08-15</t>
-        </is>
+      <c r="D113" s="2" t="n">
+        <v>22508</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2021-03-28</t>
-        </is>
+      <c r="F113" s="2" t="n">
+        <v>44283</v>
       </c>
       <c r="G113" t="n">
         <v>35650</v>
@@ -6753,13 +6985,19 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>NATATION</t>
         </is>
+      </c>
+      <c r="M113" t="n">
+        <v>11.616</v>
+      </c>
+      <c r="N113" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -6776,20 +7014,16 @@
           <t>Luc</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>1973-08-05</t>
-        </is>
+      <c r="D114" s="2" t="n">
+        <v>26881</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2021-01-29</t>
-        </is>
+      <c r="F114" s="2" t="n">
+        <v>44225</v>
       </c>
       <c r="G114" t="n">
         <v>56020</v>
@@ -6809,13 +7043,19 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>NATATION</t>
         </is>
+      </c>
+      <c r="M114" t="n">
+        <v>18.848</v>
+      </c>
+      <c r="N114" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -6832,20 +7072,16 @@
           <t>Gabriel</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>1961-06-03</t>
-        </is>
+      <c r="D115" s="2" t="n">
+        <v>22435</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2023-01-30</t>
-        </is>
+      <c r="F115" s="2" t="n">
+        <v>44956</v>
       </c>
       <c r="G115" t="n">
         <v>27820</v>
@@ -6865,13 +7101,19 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M115" t="n">
+        <v>12.932</v>
+      </c>
+      <c r="N115" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -6888,20 +7130,16 @@
           <t>Andréa</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>1963-04-02</t>
-        </is>
+      <c r="D116" s="2" t="n">
+        <v>23103</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2024-06-21</t>
-        </is>
+      <c r="F116" s="2" t="n">
+        <v>45464</v>
       </c>
       <c r="G116" t="n">
         <v>68430</v>
@@ -6921,13 +7159,19 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>TENNIS</t>
         </is>
+      </c>
+      <c r="M116" t="n">
+        <v>33.433</v>
+      </c>
+      <c r="N116" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -6944,20 +7188,16 @@
           <t>Théodore</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>1973-05-20</t>
-        </is>
+      <c r="D117" s="2" t="n">
+        <v>26804</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2024-05-11</t>
-        </is>
+      <c r="F117" s="2" t="n">
+        <v>45423</v>
       </c>
       <c r="G117" t="n">
         <v>52600</v>
@@ -6977,13 +7217,19 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>VOILE</t>
         </is>
+      </c>
+      <c r="M117" t="n">
+        <v>10.746</v>
+      </c>
+      <c r="N117" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -7000,20 +7246,16 @@
           <t>Benjamin</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>1994-08-02</t>
-        </is>
+      <c r="D118" s="2" t="n">
+        <v>34548</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2021-07-24</t>
-        </is>
+      <c r="F118" s="2" t="n">
+        <v>44401</v>
       </c>
       <c r="G118" t="n">
         <v>72240</v>
@@ -7033,13 +7275,19 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>RUGBY</t>
         </is>
+      </c>
+      <c r="M118" t="n">
+        <v>17.644</v>
+      </c>
+      <c r="N118" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -7056,20 +7304,16 @@
           <t>Simon</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>1987-07-11</t>
-        </is>
+      <c r="D119" s="2" t="n">
+        <v>31969</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2022-05-05</t>
-        </is>
+      <c r="F119" s="2" t="n">
+        <v>44686</v>
       </c>
       <c r="G119" t="n">
         <v>69840</v>
@@ -7089,13 +7333,19 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>BOXE</t>
         </is>
+      </c>
+      <c r="M119" t="n">
+        <v>32.898</v>
+      </c>
+      <c r="N119" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -7112,20 +7362,16 @@
           <t>Alain</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>1990-02-14</t>
-        </is>
+      <c r="D120" s="2" t="n">
+        <v>32918</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
+      <c r="F120" s="2" t="n">
+        <v>45009</v>
       </c>
       <c r="G120" t="n">
         <v>69510</v>
@@ -7145,13 +7391,19 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M120" t="n">
+        <v>28.448</v>
+      </c>
+      <c r="N120" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -7168,20 +7420,16 @@
           <t>Aurélien</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>1963-08-10</t>
-        </is>
+      <c r="D121" s="2" t="n">
+        <v>23233</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2021-10-06</t>
-        </is>
+      <c r="F121" s="2" t="n">
+        <v>44475</v>
       </c>
       <c r="G121" t="n">
         <v>73500</v>
@@ -7201,13 +7449,19 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M121" t="n">
+        <v>5.029</v>
+      </c>
+      <c r="N121" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -7224,20 +7478,16 @@
           <t>Marcelle</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>1961-02-20</t>
-        </is>
+      <c r="D122" s="2" t="n">
+        <v>22332</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2023-09-24</t>
-        </is>
+      <c r="F122" s="2" t="n">
+        <v>45193</v>
       </c>
       <c r="G122" t="n">
         <v>26970</v>
@@ -7257,13 +7507,19 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M122" t="n">
+        <v>8.906000000000001</v>
+      </c>
+      <c r="N122" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -7280,20 +7536,16 @@
           <t>Aurélie</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>1990-03-06</t>
-        </is>
+      <c r="D123" s="2" t="n">
+        <v>32938</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2024-04-07</t>
-        </is>
+      <c r="F123" s="2" t="n">
+        <v>45389</v>
       </c>
       <c r="G123" t="n">
         <v>27270</v>
@@ -7313,13 +7565,19 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M123" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="N123" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -7336,20 +7594,16 @@
           <t>Emmanuelle</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2001-06-25</t>
-        </is>
+      <c r="D124" s="2" t="n">
+        <v>37067</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2020-04-21</t>
-        </is>
+      <c r="F124" s="2" t="n">
+        <v>43942</v>
       </c>
       <c r="G124" t="n">
         <v>74310</v>
@@ -7369,13 +7623,19 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M124" t="n">
+        <v>4.858</v>
+      </c>
+      <c r="N124" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -7392,20 +7652,16 @@
           <t>Damien</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2000-04-18</t>
-        </is>
+      <c r="D125" s="2" t="n">
+        <v>36634</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2023-01-11</t>
-        </is>
+      <c r="F125" s="2" t="n">
+        <v>44937</v>
       </c>
       <c r="G125" t="n">
         <v>50580</v>
@@ -7425,13 +7681,19 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>BASKETBALL</t>
         </is>
+      </c>
+      <c r="M125" t="n">
+        <v>64.625</v>
+      </c>
+      <c r="N125" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -7448,20 +7710,16 @@
           <t>Alfred</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>1960-08-09</t>
-        </is>
+      <c r="D126" s="2" t="n">
+        <v>22137</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2023-05-22</t>
-        </is>
+      <c r="F126" s="2" t="n">
+        <v>45068</v>
       </c>
       <c r="G126" t="n">
         <v>45740</v>
@@ -7481,13 +7739,19 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>RUGBY</t>
         </is>
+      </c>
+      <c r="M126" t="n">
+        <v>32.374</v>
+      </c>
+      <c r="N126" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -7504,20 +7768,16 @@
           <t>Emmanuelle</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>1998-06-16</t>
-        </is>
+      <c r="D127" s="2" t="n">
+        <v>35962</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
-        </is>
+      <c r="F127" s="2" t="n">
+        <v>45721</v>
       </c>
       <c r="G127" t="n">
         <v>52920</v>
@@ -7537,13 +7797,19 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>FOOTBALL</t>
         </is>
+      </c>
+      <c r="M127" t="n">
+        <v>25.015</v>
+      </c>
+      <c r="N127" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -7560,20 +7826,16 @@
           <t>Lucas</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>1984-05-08</t>
-        </is>
+      <c r="D128" s="2" t="n">
+        <v>30810</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2023-12-11</t>
-        </is>
+      <c r="F128" s="2" t="n">
+        <v>45271</v>
       </c>
       <c r="G128" t="n">
         <v>53050</v>
@@ -7593,13 +7855,19 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M128" t="n">
+        <v>11.247</v>
+      </c>
+      <c r="N128" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -7616,20 +7884,16 @@
           <t>Génée</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>1980-11-29</t>
-        </is>
+      <c r="D129" s="2" t="n">
+        <v>29554</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2022-06-06</t>
-        </is>
+      <c r="F129" s="2" t="n">
+        <v>44718</v>
       </c>
       <c r="G129" t="n">
         <v>42670</v>
@@ -7649,13 +7913,19 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M129" t="n">
+        <v>35.903</v>
+      </c>
+      <c r="N129" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -7672,20 +7942,16 @@
           <t>Capucine</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2002-02-13</t>
-        </is>
+      <c r="D130" s="2" t="n">
+        <v>37300</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2024-02-18</t>
-        </is>
+      <c r="F130" s="2" t="n">
+        <v>45340</v>
       </c>
       <c r="G130" t="n">
         <v>48130</v>
@@ -7705,13 +7971,19 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M130" t="n">
+        <v>2.901</v>
+      </c>
+      <c r="N130" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -7728,20 +8000,16 @@
           <t>Daniel</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>1967-09-24</t>
-        </is>
+      <c r="D131" s="2" t="n">
+        <v>24739</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2022-07-05</t>
-        </is>
+      <c r="F131" s="2" t="n">
+        <v>44747</v>
       </c>
       <c r="G131" t="n">
         <v>62410</v>
@@ -7761,13 +8029,19 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M131" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="N131" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -7784,20 +8058,16 @@
           <t>Gégoire</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>1978-07-31</t>
-        </is>
+      <c r="D132" s="2" t="n">
+        <v>28702</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2024-12-02</t>
-        </is>
+      <c r="F132" s="2" t="n">
+        <v>45628</v>
       </c>
       <c r="G132" t="n">
         <v>33130</v>
@@ -7817,13 +8087,19 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M132" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N132" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -7840,20 +8116,16 @@
           <t>Sébastien</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>1975-02-13</t>
-        </is>
+      <c r="D133" s="2" t="n">
+        <v>27438</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2024-09-27</t>
-        </is>
+      <c r="F133" s="2" t="n">
+        <v>45562</v>
       </c>
       <c r="G133" t="n">
         <v>35320</v>
@@ -7873,13 +8145,19 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>TRIATHLON</t>
         </is>
+      </c>
+      <c r="M133" t="n">
+        <v>9.977</v>
+      </c>
+      <c r="N133" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -7896,20 +8174,16 @@
           <t>Emmanuel</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>1990-12-22</t>
-        </is>
+      <c r="D134" s="2" t="n">
+        <v>33229</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2022-06-19</t>
-        </is>
+      <c r="F134" s="2" t="n">
+        <v>44731</v>
       </c>
       <c r="G134" t="n">
         <v>37120</v>
@@ -7929,13 +8203,19 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>JUDO</t>
         </is>
+      </c>
+      <c r="M134" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="N134" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -7952,20 +8232,16 @@
           <t>William</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>1975-02-28</t>
-        </is>
+      <c r="D135" s="2" t="n">
+        <v>27453</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2021-12-23</t>
-        </is>
+      <c r="F135" s="2" t="n">
+        <v>44553</v>
       </c>
       <c r="G135" t="n">
         <v>34090</v>
@@ -7985,13 +8261,19 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>BOXE</t>
         </is>
+      </c>
+      <c r="M135" t="n">
+        <v>23.498</v>
+      </c>
+      <c r="N135" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -8008,20 +8290,16 @@
           <t>William</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>1984-01-20</t>
-        </is>
+      <c r="D136" s="2" t="n">
+        <v>30701</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2023-07-31</t>
-        </is>
+      <c r="F136" s="2" t="n">
+        <v>45138</v>
       </c>
       <c r="G136" t="n">
         <v>38460</v>
@@ -8041,13 +8319,19 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>JUDO</t>
         </is>
+      </c>
+      <c r="M136" t="n">
+        <v>48.077</v>
+      </c>
+      <c r="N136" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -8064,20 +8348,16 @@
           <t>Julie</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>1990-02-14</t>
-        </is>
+      <c r="D137" s="2" t="n">
+        <v>32918</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2023-10-07</t>
-        </is>
+      <c r="F137" s="2" t="n">
+        <v>45206</v>
       </c>
       <c r="G137" t="n">
         <v>35470</v>
@@ -8097,13 +8377,19 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M137" t="n">
+        <v>2.561</v>
+      </c>
+      <c r="N137" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -8120,20 +8406,16 @@
           <t>Bertrand</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>1988-04-26</t>
-        </is>
+      <c r="D138" s="2" t="n">
+        <v>32259</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2024-12-09</t>
-        </is>
+      <c r="F138" s="2" t="n">
+        <v>45635</v>
       </c>
       <c r="G138" t="n">
         <v>72520</v>
@@ -8153,13 +8435,19 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M138" t="n">
+        <v>10.863</v>
+      </c>
+      <c r="N138" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -8176,20 +8464,16 @@
           <t>Bertrand</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>1999-06-01</t>
-        </is>
+      <c r="D139" s="2" t="n">
+        <v>36312</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2022-05-30</t>
-        </is>
+      <c r="F139" s="2" t="n">
+        <v>44711</v>
       </c>
       <c r="G139" t="n">
         <v>69560</v>
@@ -8209,13 +8493,19 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M139" t="n">
+        <v>29.422</v>
+      </c>
+      <c r="N139" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -8232,20 +8522,16 @@
           <t>Nath</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>1994-07-26</t>
-        </is>
+      <c r="D140" s="2" t="n">
+        <v>34541</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2024-05-18</t>
-        </is>
+      <c r="F140" s="2" t="n">
+        <v>45430</v>
       </c>
       <c r="G140" t="n">
         <v>56100</v>
@@ -8265,13 +8551,19 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>NATATION</t>
         </is>
+      </c>
+      <c r="M140" t="n">
+        <v>5.276</v>
+      </c>
+      <c r="N140" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -8288,20 +8580,16 @@
           <t>Juliette</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>1978-06-14</t>
-        </is>
+      <c r="D141" s="2" t="n">
+        <v>28655</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2022-10-06</t>
-        </is>
+      <c r="F141" s="2" t="n">
+        <v>44840</v>
       </c>
       <c r="G141" t="n">
         <v>55910</v>
@@ -8321,13 +8609,19 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>BADMINTON</t>
         </is>
+      </c>
+      <c r="M141" t="n">
+        <v>25.015</v>
+      </c>
+      <c r="N141" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -8344,20 +8638,16 @@
           <t>Simone</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>1981-10-29</t>
-        </is>
+      <c r="D142" s="2" t="n">
+        <v>29888</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
+      <c r="F142" s="2" t="n">
+        <v>44805</v>
       </c>
       <c r="G142" t="n">
         <v>65640</v>
@@ -8377,13 +8667,19 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M142" t="n">
+        <v>11.626</v>
+      </c>
+      <c r="N142" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -8400,20 +8696,16 @@
           <t>Alain</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>1977-09-23</t>
-        </is>
+      <c r="D143" s="2" t="n">
+        <v>28391</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2022-10-07</t>
-        </is>
+      <c r="F143" s="2" t="n">
+        <v>44841</v>
       </c>
       <c r="G143" t="n">
         <v>58380</v>
@@ -8433,13 +8725,19 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M143" t="n">
+        <v>23.701</v>
+      </c>
+      <c r="N143" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -8456,20 +8754,16 @@
           <t>Joseph</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>1966-01-29</t>
-        </is>
+      <c r="D144" s="2" t="n">
+        <v>24136</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2024-02-25</t>
-        </is>
+      <c r="F144" s="2" t="n">
+        <v>45347</v>
       </c>
       <c r="G144" t="n">
         <v>30880</v>
@@ -8489,13 +8783,19 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M144" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="N144" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -8512,20 +8812,16 @@
           <t>Claire</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>1986-03-16</t>
-        </is>
+      <c r="D145" s="2" t="n">
+        <v>31487</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2023-08-22</t>
-        </is>
+      <c r="F145" s="2" t="n">
+        <v>45160</v>
       </c>
       <c r="G145" t="n">
         <v>54170</v>
@@ -8545,13 +8841,19 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>TENNIS</t>
         </is>
+      </c>
+      <c r="M145" t="n">
+        <v>40.066</v>
+      </c>
+      <c r="N145" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -8568,20 +8870,16 @@
           <t>Anais</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>1962-12-07</t>
-        </is>
+      <c r="D146" s="2" t="n">
+        <v>22987</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2023-02-17</t>
-        </is>
+      <c r="F146" s="2" t="n">
+        <v>44974</v>
       </c>
       <c r="G146" t="n">
         <v>46210</v>
@@ -8601,13 +8899,19 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M146" t="n">
+        <v>17.012</v>
+      </c>
+      <c r="N146" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -8624,20 +8928,16 @@
           <t>Suzanne</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>1971-07-07</t>
-        </is>
+      <c r="D147" s="2" t="n">
+        <v>26121</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2022-09-01</t>
-        </is>
+      <c r="F147" s="2" t="n">
+        <v>44805</v>
       </c>
       <c r="G147" t="n">
         <v>48040</v>
@@ -8657,13 +8957,19 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>TRIATHLON</t>
         </is>
+      </c>
+      <c r="M147" t="n">
+        <v>9.856</v>
+      </c>
+      <c r="N147" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -8680,20 +8986,16 @@
           <t>Marie</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>1961-01-01</t>
-        </is>
+      <c r="D148" s="2" t="n">
+        <v>22282</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2022-06-06</t>
-        </is>
+      <c r="F148" s="2" t="n">
+        <v>44718</v>
       </c>
       <c r="G148" t="n">
         <v>39050</v>
@@ -8713,13 +9015,19 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M148" t="n">
+        <v>66.218</v>
+      </c>
+      <c r="N148" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -8736,20 +9044,16 @@
           <t>Roger</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>1987-04-18</t>
-        </is>
+      <c r="D149" s="2" t="n">
+        <v>31885</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2022-02-19</t>
-        </is>
+      <c r="F149" s="2" t="n">
+        <v>44611</v>
       </c>
       <c r="G149" t="n">
         <v>49230</v>
@@ -8769,13 +9073,19 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>RANDONNÉE</t>
         </is>
+      </c>
+      <c r="M149" t="n">
+        <v>3.322</v>
+      </c>
+      <c r="N149" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -8792,20 +9102,16 @@
           <t>Laurence</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2001-07-05</t>
-        </is>
+      <c r="D150" s="2" t="n">
+        <v>37077</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2021-06-14</t>
-        </is>
+      <c r="F150" s="2" t="n">
+        <v>44361</v>
       </c>
       <c r="G150" t="n">
         <v>63450</v>
@@ -8825,13 +9131,19 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>RUGBY</t>
         </is>
+      </c>
+      <c r="M150" t="n">
+        <v>4.595</v>
+      </c>
+      <c r="N150" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -8848,20 +9160,16 @@
           <t>Marguerite</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2000-06-09</t>
-        </is>
+      <c r="D151" s="2" t="n">
+        <v>36686</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2023-10-19</t>
-        </is>
+      <c r="F151" s="2" t="n">
+        <v>45218</v>
       </c>
       <c r="G151" t="n">
         <v>54220</v>
@@ -8881,13 +9189,19 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M151" t="n">
+        <v>3.143</v>
+      </c>
+      <c r="N151" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -8904,20 +9218,16 @@
           <t>René</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>1961-06-10</t>
-        </is>
+      <c r="D152" s="2" t="n">
+        <v>22442</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2023-08-24</t>
-        </is>
+      <c r="F152" s="2" t="n">
+        <v>45162</v>
       </c>
       <c r="G152" t="n">
         <v>68300</v>
@@ -8937,13 +9247,19 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Transports en commun</t>
+          <t>TRANSPORTS EN COMMUN</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M152" t="n">
+        <v>10.061</v>
+      </c>
+      <c r="N152" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -8960,20 +9276,16 @@
           <t>Nathalie</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>1970-12-30</t>
-        </is>
+      <c r="D153" s="2" t="n">
+        <v>25932</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2023-04-19</t>
-        </is>
+      <c r="F153" s="2" t="n">
+        <v>45035</v>
       </c>
       <c r="G153" t="n">
         <v>31820</v>
@@ -8993,13 +9305,19 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M153" t="n">
+        <v>18.495</v>
+      </c>
+      <c r="N153" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -9016,20 +9334,16 @@
           <t>Margaud</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>1992-05-23</t>
-        </is>
+      <c r="D154" s="2" t="n">
+        <v>33747</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2022-03-29</t>
-        </is>
+      <c r="F154" s="2" t="n">
+        <v>44649</v>
       </c>
       <c r="G154" t="n">
         <v>67480</v>
@@ -9049,13 +9363,19 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>RUGBY</t>
         </is>
+      </c>
+      <c r="M154" t="n">
+        <v>12.894</v>
+      </c>
+      <c r="N154" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -9072,20 +9392,16 @@
           <t>TimothÃ©e</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>1986-06-15</t>
-        </is>
+      <c r="D155" s="2" t="n">
+        <v>31578</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2024-02-07</t>
-        </is>
+      <c r="F155" s="2" t="n">
+        <v>45329</v>
       </c>
       <c r="G155" t="n">
         <v>54180</v>
@@ -9105,13 +9421,19 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M155" t="n">
+        <v>1.628</v>
+      </c>
+      <c r="N155" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -9128,20 +9450,16 @@
           <t>Michel</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>1994-10-26</t>
-        </is>
+      <c r="D156" s="2" t="n">
+        <v>34633</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2025-01-10</t>
-        </is>
+      <c r="F156" s="2" t="n">
+        <v>45667</v>
       </c>
       <c r="G156" t="n">
         <v>26320</v>
@@ -9161,13 +9479,19 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M156" t="n">
+        <v>10.145</v>
+      </c>
+      <c r="N156" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -9184,20 +9508,16 @@
           <t>Sylvain</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>1982-11-29</t>
-        </is>
+      <c r="D157" s="2" t="n">
+        <v>30284</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2024-04-11</t>
-        </is>
+      <c r="F157" s="2" t="n">
+        <v>45393</v>
       </c>
       <c r="G157" t="n">
         <v>60200</v>
@@ -9217,13 +9537,19 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M157" t="n">
+        <v>10.016</v>
+      </c>
+      <c r="N157" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -9240,20 +9566,16 @@
           <t>Gilles</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1986-12-23</t>
-        </is>
+      <c r="D158" s="2" t="n">
+        <v>31769</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
+      <c r="F158" s="2" t="n">
+        <v>45715</v>
       </c>
       <c r="G158" t="n">
         <v>59910</v>
@@ -9273,13 +9595,19 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M158" t="n">
+        <v>11.251</v>
+      </c>
+      <c r="N158" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -9296,20 +9624,16 @@
           <t>Jeannine</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>1966-06-24</t>
-        </is>
+      <c r="D159" s="2" t="n">
+        <v>24282</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2022-01-22</t>
-        </is>
+      <c r="F159" s="2" t="n">
+        <v>44583</v>
       </c>
       <c r="G159" t="n">
         <v>48430</v>
@@ -9329,13 +9653,19 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Marche/running</t>
+          <t>MARCHE/RUNNING</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>TENNIS</t>
         </is>
+      </c>
+      <c r="M159" t="n">
+        <v>5.018</v>
+      </c>
+      <c r="N159" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -9352,20 +9682,16 @@
           <t>Philippe</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>1996-09-10</t>
-        </is>
+      <c r="D160" s="2" t="n">
+        <v>35318</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2020-11-27</t>
-        </is>
+      <c r="F160" s="2" t="n">
+        <v>44162</v>
       </c>
       <c r="G160" t="n">
         <v>56380</v>
@@ -9385,13 +9711,19 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>RUNING</t>
         </is>
+      </c>
+      <c r="M160" t="n">
+        <v>10.495</v>
+      </c>
+      <c r="N160" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -9408,20 +9740,16 @@
           <t>Odette</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>1960-12-22</t>
-        </is>
+      <c r="D161" s="2" t="n">
+        <v>22272</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>Ventes</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2023-04-08</t>
-        </is>
+      <c r="F161" s="2" t="n">
+        <v>45024</v>
       </c>
       <c r="G161" t="n">
         <v>45170</v>
@@ -9441,13 +9769,19 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>véhicule thermique/électrique</t>
+          <t>VÉHICULE THERMIQUE/ÉLECTRIQUE</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>AUCUN</t>
         </is>
+      </c>
+      <c r="M161" t="n">
+        <v>12.975</v>
+      </c>
+      <c r="N161" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -9464,20 +9798,16 @@
           <t>Henri</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>1973-11-16</t>
-        </is>
+      <c r="D162" s="2" t="n">
+        <v>26984</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2025-01-24</t>
-        </is>
+      <c r="F162" s="2" t="n">
+        <v>45681</v>
       </c>
       <c r="G162" t="n">
         <v>64180</v>
@@ -9497,7 +9827,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Vélo/Trottinette/Autres</t>
+          <t>VÉLO/TROTTINETTE/AUTRES</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -9505,8 +9835,14 @@
           <t>NATATION</t>
         </is>
       </c>
+      <c r="M162" t="n">
+        <v>10.373</v>
+      </c>
+      <c r="N162" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>